--- a/data_lake/descensos_temperatura/dt=2026-07-29/excel/PronosticoMunicipal_DescensosTemperatura_72h.xlsx
+++ b/data_lake/descensos_temperatura/dt=2026-07-29/excel/PronosticoMunicipal_DescensosTemperatura_72h.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K173"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,17 +488,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -506,12 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Puerres</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,17 +541,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -559,12 +559,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -612,12 +612,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>52287</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ipiales</t>
+          <t>Funes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -665,12 +665,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Cuaspud</t>
+          <t>Cumbal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -679,11 +679,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -700,17 +700,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -718,12 +718,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>52573</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Puerres</t>
+          <t>Sapuyes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -771,12 +771,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>52788</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Aldana</t>
+          <t>Tangua</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,17 +806,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -824,12 +824,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>52001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pupiales</t>
+          <t>Pasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -877,12 +877,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>Mallama</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -912,17 +912,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -930,17 +930,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>52287</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Funes</t>
+          <t>Uribe</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -965,17 +965,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -983,25 +983,25 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Cubarral</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>73686</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sapuyes</t>
+          <t>Santa Isabel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>86760</t>
+          <t>73461</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Murillo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Putumayo</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1142,17 +1142,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>52788</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tangua</t>
+          <t>Villamaria</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1195,17 +1195,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>52838</t>
+          <t>73870</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Túquerres</t>
+          <t>Villahermosa</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1230,17 +1230,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>68318</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pasto</t>
+          <t>Guaca</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>68705</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Mallama</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>52110</t>
+          <t>54174</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Buesaco</t>
+          <t>Chitagá</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1389,17 +1389,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-29 19:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-30 07:00</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1407,17 +1407,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>52699</t>
+          <t>54743</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Silos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>52378</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1495,17 +1495,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Cumbal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1548,17 +1548,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>San Sebastián</t>
+          <t>Teruel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19397</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>La Vega</t>
+          <t>Páez</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>San Agustín</t>
+          <t>Toribío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>73555</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Saladoblanco</t>
+          <t>Planadas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Isnos</t>
+          <t>Uribe</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1831,25 +1831,25 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>50400</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>La Argentina</t>
+          <t>Lejanías</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1866,17 +1866,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1884,17 +1884,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>00000</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Area En Litigio Cauca - Huila</t>
+          <t>Cubarral</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>50318</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sotará</t>
+          <t>Guamal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Puracé</t>
+          <t>Gutiérrez</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2025,17 +2025,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Popayán</t>
+          <t>Une</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2078,17 +2078,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Totoró</t>
+          <t>Bogotá, D.C.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Inzá</t>
+          <t>Aquitania</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2184,17 +2184,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2202,17 +2202,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Silvia</t>
+          <t>Monguí</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2255,25 +2255,25 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>Sogamoso</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2290,17 +2290,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2308,25 +2308,25 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Páez</t>
+          <t>Mongua</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2343,17 +2343,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2361,25 +2361,25 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Toribío</t>
+          <t>Tópaga</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2414,25 +2414,25 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Corinto</t>
+          <t>Gámeza</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2449,17 +2449,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Corrales</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2520,25 +2520,25 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Planadas</t>
+          <t>Tasco</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2573,17 +2573,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>76275</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Cerinza</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2608,17 +2608,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2626,17 +2626,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Rioblanco</t>
+          <t>Santa Rosa De Viterbo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Uribe</t>
+          <t>Duitama</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2714,17 +2714,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Lejanías</t>
+          <t>Socha</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -2820,17 +2820,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cubarral</t>
+          <t>Socotá</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Tutazá</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>68264</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Chaparral</t>
+          <t>Encino</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2979,17 +2979,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Guamal</t>
+          <t>Chita</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -3050,25 +3050,25 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>85136</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>La Salina</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Casanare</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3085,17 +3085,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>73622</t>
+          <t>68217</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Roncesvalles</t>
+          <t>Coromoro</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3138,17 +3138,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3156,25 +3156,25 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Gutiérrez</t>
+          <t>El Cocuy</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3209,17 +3209,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Génova</t>
+          <t>Onzaga</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3244,17 +3244,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -3262,17 +3262,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>76736</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>El Espino</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Une</t>
+          <t>Tame</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3350,17 +3350,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -3368,25 +3368,25 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Chipaque</t>
+          <t>Güicán De La Sierra</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3403,17 +3403,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-30 19:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-07-31 07:00</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3421,25 +3421,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Chiscas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3456,17 +3456,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -3474,25 +3474,25 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>63690</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Salento</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -3509,17 +3509,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -3527,25 +3527,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>73043</t>
+          <t>52356</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Ipiales</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -3562,17 +3562,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -3580,25 +3580,25 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Santa Isabel</t>
+          <t>Cuaspud</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3615,17 +3615,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -3633,17 +3633,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bogotá, D.C.</t>
+          <t>Puerres</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -3686,25 +3686,25 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Murillo</t>
+          <t>Aldana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3721,17 +3721,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>66682</t>
+          <t>52585</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Pupiales</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -3774,17 +3774,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -3792,25 +3792,25 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Villamaria</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -3845,17 +3845,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>52287</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Villahermosa</t>
+          <t>Funes</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -3880,17 +3880,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -3898,25 +3898,25 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>73152</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Casabianca</t>
+          <t>Cumbal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3933,17 +3933,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>73347</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Herveo</t>
+          <t>Sapuyes</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -4004,17 +4004,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>52788</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Aquitania</t>
+          <t>Tangua</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -4039,17 +4039,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -4057,25 +4057,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Monguí</t>
+          <t>Túquerres</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -4092,17 +4092,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -4110,17 +4110,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>52001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sogamoso</t>
+          <t>Pasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4145,17 +4145,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -4163,17 +4163,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Mongua</t>
+          <t>Mallama</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4198,17 +4198,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>52378</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Gámeza</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4269,17 +4269,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tasco</t>
+          <t>Santa Rosa</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4304,17 +4304,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -4322,17 +4322,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Cerinza</t>
+          <t>San Sebastián</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4357,17 +4357,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4375,17 +4375,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Santa Rosa De Viterbo</t>
+          <t>La Vega</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4410,17 +4410,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Duitama</t>
+          <t>San Agustín</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Socha</t>
+          <t>Saladoblanco</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4516,17 +4516,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -4534,17 +4534,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>41359</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Isnos</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Socotá</t>
+          <t>La Argentina</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4622,17 +4622,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>00000</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tutazá</t>
+          <t>Area En Litigio Cauca - Huila</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4675,17 +4675,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -4693,17 +4693,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>68264</t>
+          <t>19760</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Encino</t>
+          <t>Sotará</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -4728,17 +4728,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -4746,17 +4746,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Chita</t>
+          <t>Puracé</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -4799,17 +4799,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>85136</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>La Salina</t>
+          <t>Totoró</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Casanare</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -4834,17 +4834,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -4852,17 +4852,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>68217</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Coromoro</t>
+          <t>Inzá</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J84" t="n">
@@ -4887,17 +4887,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -4905,17 +4905,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>El Cocuy</t>
+          <t>Silvia</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -4940,17 +4940,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -4958,17 +4958,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Teruel</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Guacamayas</t>
+          <t>Jambaló</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -5046,17 +5046,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -5064,17 +5064,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Panqueba</t>
+          <t>Páez</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -5099,17 +5099,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5117,17 +5117,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>68502</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Onzaga</t>
+          <t>Toribío</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -5152,17 +5152,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -5170,25 +5170,25 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>19212</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>El Espino</t>
+          <t>Corinto</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5205,17 +5205,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5223,25 +5223,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>73555</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tame</t>
+          <t>Planadas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5258,17 +5258,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>68152</t>
+          <t>73616</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Carcasí</t>
+          <t>Rioblanco</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5311,17 +5311,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5329,25 +5329,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Güicán De La Sierra</t>
+          <t>Uribe</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5364,17 +5364,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -5382,25 +5382,25 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>50400</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Chiscas</t>
+          <t>Lejanías</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5417,17 +5417,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5435,17 +5435,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>81300</t>
+          <t>41206</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Fortul</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -5470,17 +5470,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -5488,17 +5488,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>68207</t>
+          <t>76111</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5523,17 +5523,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -5541,17 +5541,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>68162</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Cerrito</t>
+          <t>Cubarral</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -5576,17 +5576,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -5594,17 +5594,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Cubará</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -5629,17 +5629,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -5647,17 +5647,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>68318</t>
+          <t>73168</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Guaca</t>
+          <t>Chaparral</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -5700,17 +5700,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>68705</t>
+          <t>50318</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Guamal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -5735,17 +5735,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -5753,17 +5753,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>68820</t>
+          <t>76834</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tona</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>54174</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Chitagá</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Norte de Santander</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -5841,17 +5841,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -5859,17 +5859,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>73622</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Silos</t>
+          <t>Roncesvalles</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Norte de Santander</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -5894,17 +5894,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -5912,17 +5912,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>54480</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Mutiscua</t>
+          <t>Arbeláez</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Norte de Santander</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -5947,17 +5947,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-28 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -5965,17 +5965,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>68867</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Vetas</t>
+          <t>Gutiérrez</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -6000,17 +6000,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -6018,25 +6018,25 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Ipiales</t>
+          <t>Génova</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -6053,17 +6053,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -6071,17 +6071,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>Pasca</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -6106,17 +6106,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>76736</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -6177,17 +6177,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sapuyes</t>
+          <t>Une</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -6212,17 +6212,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6230,17 +6230,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Mallama</t>
+          <t>Chipaque</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6265,17 +6265,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Santa Isabel</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6318,17 +6318,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>73043</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Murillo</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6371,17 +6371,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-07-29 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-07-30 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -6389,17 +6389,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>73686</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Villamaria</t>
+          <t>Santa Isabel</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6424,17 +6424,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -6442,17 +6442,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Aldana</t>
+          <t>Bogotá, D.C.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6477,17 +6477,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -6495,17 +6495,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>73461</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Pupiales</t>
+          <t>Murillo</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -6530,17 +6530,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -6548,17 +6548,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>73870</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>Villahermosa</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -6601,25 +6601,25 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Tame</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -6636,17 +6636,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -6654,17 +6654,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sapuyes</t>
+          <t>Güicán De La Sierra</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -6689,17 +6689,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-30 19:00</t>
+          <t>2026-07-31 19:00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-01 07:00</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -6707,2885 +6707,23 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>52838</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Túquerres</t>
+          <t>Chiscas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J119" t="n">
         <v>3</v>
       </c>
       <c r="K119" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>12</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>52435</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Mallama</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>3</v>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>12</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>19701</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Santa Rosa</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v>3</v>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>12</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>19693</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>San Sebastián</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v>3</v>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>12</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>19397</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>La Vega</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>3</v>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>12</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>41668</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>San Agustín</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Huila</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>3</v>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>12</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>41660</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Saladoblanco</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Huila</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>3</v>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>12</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>41359</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Isnos</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Huila</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>3</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>12</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Area En Litigio Cauca - Huila</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J127" t="n">
-        <v>3</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>12</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>19760</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sotará</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J128" t="n">
-        <v>3</v>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>12</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>19585</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Puracé</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J129" t="n">
-        <v>3</v>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
-        <v>12</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>19824</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Totoró</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J130" t="n">
-        <v>3</v>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>12</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>19355</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Inzá</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J131" t="n">
-        <v>3</v>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F132" t="n">
-        <v>12</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>19743</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Silvia</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J132" t="n">
-        <v>3</v>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>12</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>41801</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Teruel</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Huila</t>
-        </is>
-      </c>
-      <c r="J133" t="n">
-        <v>3</v>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
-        <v>12</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>19517</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Páez</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J134" t="n">
-        <v>3</v>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F135" t="n">
-        <v>12</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>19821</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Toribío</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J135" t="n">
-        <v>3</v>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F136" t="n">
-        <v>12</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>19212</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Corinto</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J136" t="n">
-        <v>3</v>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F137" t="n">
-        <v>12</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>73555</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Planadas</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="J137" t="n">
-        <v>3</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
-        <v>12</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>73616</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Rioblanco</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="J138" t="n">
-        <v>3</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
-        <v>12</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>50370</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Uribe</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="J139" t="n">
-        <v>3</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F140" t="n">
-        <v>12</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>50400</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Lejanías</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="J140" t="n">
-        <v>3</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F141" t="n">
-        <v>12</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>41206</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Huila</t>
-        </is>
-      </c>
-      <c r="J141" t="n">
-        <v>3</v>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F142" t="n">
-        <v>12</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>50223</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Cubarral</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="J142" t="n">
-        <v>4</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F143" t="n">
-        <v>12</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>25120</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Cabrera</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="J143" t="n">
-        <v>3</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F144" t="n">
-        <v>12</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>73168</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Chaparral</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="J144" t="n">
-        <v>3</v>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F145" t="n">
-        <v>12</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>50318</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Guamal</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="J145" t="n">
-        <v>3</v>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F146" t="n">
-        <v>12</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>25649</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>San Bernardo</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="J146" t="n">
-        <v>3</v>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F147" t="n">
-        <v>12</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>73622</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Roncesvalles</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="J147" t="n">
-        <v>3</v>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>12</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>25053</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Arbeláez</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="J148" t="n">
-        <v>3</v>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F149" t="n">
-        <v>12</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>25339</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Gutiérrez</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="J149" t="n">
-        <v>3</v>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>12</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>63302</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Génova</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Quindío</t>
-        </is>
-      </c>
-      <c r="J150" t="n">
-        <v>3</v>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F151" t="n">
-        <v>12</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>25535</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Pasca</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="J151" t="n">
-        <v>3</v>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v>12</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>25845</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Une</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="J152" t="n">
-        <v>3</v>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>12</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>25178</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Chipaque</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="J153" t="n">
-        <v>3</v>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F154" t="n">
-        <v>12</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>25377</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>La Calera</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="J154" t="n">
-        <v>3</v>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>12</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>11001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Bogotá, D.C.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="J155" t="n">
-        <v>4</v>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>12</v>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>25322</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Guasca</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="J156" t="n">
-        <v>3</v>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>12</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>15047</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Aquitania</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J157" t="n">
-        <v>3</v>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F158" t="n">
-        <v>12</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>15466</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Monguí</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J158" t="n">
-        <v>3</v>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F159" t="n">
-        <v>12</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>15759</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sogamoso</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J159" t="n">
-        <v>3</v>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F160" t="n">
-        <v>12</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>15464</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Mongua</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J160" t="n">
-        <v>3</v>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F161" t="n">
-        <v>12</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>15820</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Tópaga</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J161" t="n">
-        <v>3</v>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F162" t="n">
-        <v>12</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>15296</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Gámeza</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J162" t="n">
-        <v>3</v>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F163" t="n">
-        <v>12</v>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>15790</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Tasco</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J163" t="n">
-        <v>3</v>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F164" t="n">
-        <v>12</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>15757</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Socha</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J164" t="n">
-        <v>3</v>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>12</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>15755</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Socotá</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J165" t="n">
-        <v>3</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F166" t="n">
-        <v>12</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>15183</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Chita</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J166" t="n">
-        <v>3</v>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F167" t="n">
-        <v>12</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>85136</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>La Salina</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Casanare</t>
-        </is>
-      </c>
-      <c r="J167" t="n">
-        <v>4</v>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v>12</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>15244</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>El Cocuy</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J168" t="n">
-        <v>4</v>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F169" t="n">
-        <v>12</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>15248</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>El Espino</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J169" t="n">
-        <v>3</v>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
-        <v>12</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>81794</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Tame</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="J170" t="n">
-        <v>4</v>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v>12</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>15332</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Güicán De La Sierra</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J171" t="n">
-        <v>4</v>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v>12</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>15180</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Chiscas</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J172" t="n">
-        <v>4</v>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2026-07-30 19:00</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>2026-07-31 07:00</t>
-        </is>
-      </c>
-      <c r="F173" t="n">
-        <v>12</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>81300</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Fortul</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="J173" t="n">
-        <v>3</v>
-      </c>
-      <c r="K173" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
